--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run4/epoch_70/per_file_predictions_epoch_70.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run4/epoch_70/per_file_predictions_epoch_70.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,784 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.6594,0.3064,0.0228,0.0340</t>
-  </si>
-  <si>
-    <t>0.0041,0.0203,0.0010,0.9954</t>
-  </si>
-  <si>
-    <t>0.9267,0.0080,0.0045,0.0561</t>
-  </si>
-  <si>
-    <t>0.5434,0.0024,0.0022,0.6319</t>
-  </si>
-  <si>
-    <t>0.9979,0.0005,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9921,0.0036,0.0021,0.0014</t>
-  </si>
-  <si>
-    <t>0.9941,0.0008,0.0041,0.0006</t>
-  </si>
-  <si>
-    <t>0.9980,0.0004,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9804,0.0136,0.0013,0.0037</t>
-  </si>
-  <si>
-    <t>0.9926,0.0054,0.0004,0.0006</t>
-  </si>
-  <si>
-    <t>0.9916,0.0048,0.0015,0.0010</t>
-  </si>
-  <si>
-    <t>0.9951,0.0011,0.0010,0.0013</t>
-  </si>
-  <si>
-    <t>0.9096,0.0153,0.0818,0.0008</t>
-  </si>
-  <si>
-    <t>0.5936,0.0166,0.4761,0.0064</t>
-  </si>
-  <si>
-    <t>0.2642,0.0024,0.8768,0.0001</t>
-  </si>
-  <si>
-    <t>0.2142,0.0196,0.8110,0.0022</t>
-  </si>
-  <si>
-    <t>0.9189,0.0107,0.0882,0.0019</t>
-  </si>
-  <si>
-    <t>0.0034,0.9954,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.0106,0.9866,0.0020,0.0009</t>
-  </si>
-  <si>
-    <t>0.0658,0.9435,0.0033,0.0015</t>
-  </si>
-  <si>
-    <t>0.0039,0.9943,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.0009,0.9971,0.0017,0.0009</t>
-  </si>
-  <si>
-    <t>0.0684,0.0010,0.9429,0.0026</t>
-  </si>
-  <si>
-    <t>0.5241,0.0032,0.6138,0.0022</t>
-  </si>
-  <si>
-    <t>0.0006,0.0012,0.9985,0.0002</t>
-  </si>
-  <si>
-    <t>0.0040,0.0050,0.9924,0.0003</t>
-  </si>
-  <si>
-    <t>0.0156,0.0011,0.9874,0.0013</t>
-  </si>
-  <si>
-    <t>0.0056,0.0004,0.9925,0.0012</t>
-  </si>
-  <si>
-    <t>0.0009,0.0005,0.9975,0.0006</t>
-  </si>
-  <si>
-    <t>0.8429,0.2252,0.0029,0.0004</t>
-  </si>
-  <si>
-    <t>0.5939,0.1272,0.2437,0.0070</t>
-  </si>
-  <si>
-    <t>0.0012,0.0100,0.9973,0.0009</t>
-  </si>
-  <si>
-    <t>0.0028,0.9123,0.5821,0.0002</t>
-  </si>
-  <si>
-    <t>0.9581,0.0282,0.0062,0.0043</t>
-  </si>
-  <si>
-    <t>0.2697,0.0195,0.8264,0.0083</t>
-  </si>
-  <si>
-    <t>0.2344,0.7562,0.0431,0.0056</t>
-  </si>
-  <si>
-    <t>0.0049,0.9840,0.1760,0.0012</t>
-  </si>
-  <si>
-    <t>0.0046,0.5222,0.6655,0.0065</t>
-  </si>
-  <si>
-    <t>0.0675,0.0145,0.9434,0.0024</t>
-  </si>
-  <si>
-    <t>0.2533,0.0157,0.7854,0.0016</t>
-  </si>
-  <si>
-    <t>0.0051,0.0007,0.9497,0.0541</t>
-  </si>
-  <si>
-    <t>0.0046,0.0288,0.9919,0.0006</t>
-  </si>
-  <si>
-    <t>0.0012,0.9918,0.0027,0.0003</t>
-  </si>
-  <si>
-    <t>0.0029,0.0056,0.9947,0.0004</t>
-  </si>
-  <si>
-    <t>0.0251,0.7929,0.0610,0.8003</t>
-  </si>
-  <si>
-    <t>0.0025,0.9442,0.0229,0.0272</t>
-  </si>
-  <si>
-    <t>0.0002,0.9965,0.0048,0.0067</t>
-  </si>
-  <si>
-    <t>0.0004,0.9931,0.0351,0.0028</t>
-  </si>
-  <si>
-    <t>0.0003,0.0053,0.9978,0.0015</t>
-  </si>
-  <si>
-    <t>0.0008,0.8529,0.9909,0.0005</t>
-  </si>
-  <si>
-    <t>0.0040,0.0009,0.9922,0.0012</t>
-  </si>
-  <si>
-    <t>0.0039,0.0004,0.9961,0.0005</t>
-  </si>
-  <si>
-    <t>0.0041,0.0263,0.9907,0.0012</t>
-  </si>
-  <si>
-    <t>0.0088,0.1155,0.9569,0.0017</t>
-  </si>
-  <si>
-    <t>0.9756,0.0260,0.0015,0.0015</t>
-  </si>
-  <si>
-    <t>0.9697,0.0175,0.0101,0.0046</t>
-  </si>
-  <si>
-    <t>0.9546,0.0527,0.0036,0.0015</t>
-  </si>
-  <si>
-    <t>0.0056,0.0120,0.9947,0.0011</t>
-  </si>
-  <si>
-    <t>0.9873,0.0044,0.0042,0.0028</t>
-  </si>
-  <si>
-    <t>0.9950,0.0032,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.9851,0.0085,0.0027,0.0016</t>
-  </si>
-  <si>
-    <t>0.0003,0.9780,0.9374,0.0001</t>
-  </si>
-  <si>
-    <t>0.0137,0.1059,0.9721,0.0046</t>
-  </si>
-  <si>
-    <t>0.0031,0.0134,0.9925,0.0021</t>
-  </si>
-  <si>
-    <t>0.0008,0.9794,0.9476,0.0010</t>
-  </si>
-  <si>
-    <t>0.0003,0.0008,0.9967,0.0085</t>
-  </si>
-  <si>
-    <t>0.0128,0.9727,0.0147,0.0012</t>
-  </si>
-  <si>
-    <t>0.0014,0.9966,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.8871,0.0015,0.1970,0.0020</t>
-  </si>
-  <si>
-    <t>0.1027,0.0509,0.9034,0.0064</t>
-  </si>
-  <si>
-    <t>0.0067,0.0044,0.9922,0.0015</t>
-  </si>
-  <si>
-    <t>0.0011,0.9867,0.5899,0.0006</t>
-  </si>
-  <si>
-    <t>0.0014,0.9772,0.6209,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.9976,0.0264,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.9647,0.8711,0.0003</t>
-  </si>
-  <si>
-    <t>0.0219,0.0050,0.1134,0.9414</t>
-  </si>
-  <si>
-    <t>0.0006,0.0064,0.0008,0.9989</t>
-  </si>
-  <si>
-    <t>0.0003,0.0007,0.0013,0.9989</t>
-  </si>
-  <si>
-    <t>0.0018,0.0019,0.0018,0.9979</t>
-  </si>
-  <si>
-    <t>0.0016,0.0011,0.0054,0.9969</t>
-  </si>
-  <si>
-    <t>0.0010,0.0004,0.0026,0.9980</t>
-  </si>
-  <si>
-    <t>0.0001,0.9981,0.6832,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.9644,0.9747,0.0003</t>
-  </si>
-  <si>
-    <t>0.0056,0.8152,0.4921,0.0010</t>
-  </si>
-  <si>
-    <t>0.0010,0.7211,0.9799,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.9915,0.9618,0.0000</t>
-  </si>
-  <si>
-    <t>0.0240,0.9083,0.3313,0.0044</t>
-  </si>
-  <si>
-    <t>0.9916,0.0052,0.0014,0.0004</t>
-  </si>
-  <si>
-    <t>0.9938,0.0044,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9913,0.0081,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.9882,0.0086,0.0011,0.0017</t>
-  </si>
-  <si>
-    <t>0.9288,0.0919,0.0032,0.0021</t>
-  </si>
-  <si>
-    <t>0.9883,0.0117,0.0005,0.0008</t>
-  </si>
-  <si>
-    <t>0.9841,0.0160,0.0012,0.0013</t>
-  </si>
-  <si>
-    <t>0.9813,0.0083,0.0069,0.0025</t>
-  </si>
-  <si>
-    <t>0.9983,0.0003,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9958,0.0017,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.9987,0.0003,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9974,0.0004,0.0002,0.0012</t>
-  </si>
-  <si>
-    <t>0.9838,0.0136,0.0011,0.0011</t>
-  </si>
-  <si>
-    <t>0.9977,0.0002,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.9934,0.0008,0.0036,0.0014</t>
-  </si>
-  <si>
-    <t>0.0008,0.0005,0.9909,0.0249</t>
-  </si>
-  <si>
-    <t>0.0083,0.0065,0.9833,0.0072</t>
-  </si>
-  <si>
-    <t>0.9678,0.0029,0.0198,0.0019</t>
-  </si>
-  <si>
-    <t>0.0203,0.0007,0.9887,0.0004</t>
-  </si>
-  <si>
-    <t>0.0168,0.9809,0.0012,0.0009</t>
-  </si>
-  <si>
-    <t>0.0004,0.9985,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.0133,0.9725,0.0023,0.0096</t>
-  </si>
-  <si>
-    <t>0.0047,0.9909,0.0014,0.0019</t>
-  </si>
-  <si>
-    <t>0.0015,0.9973,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.0032,0.9926,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.5465,0.5335,0.0084,0.0016</t>
-  </si>
-  <si>
-    <t>0.8361,0.0330,0.0864,0.0151</t>
-  </si>
-  <si>
-    <t>0.5067,0.0223,0.5667,0.0084</t>
-  </si>
-  <si>
-    <t>0.5705,0.0135,0.4548,0.0060</t>
-  </si>
-  <si>
-    <t>0.8906,0.0020,0.1556,0.0010</t>
-  </si>
-  <si>
-    <t>0.1146,0.0346,0.7878,0.1185</t>
-  </si>
-  <si>
-    <t>0.0008,0.9958,0.0095,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.9942,0.0096,0.0020</t>
-  </si>
-  <si>
-    <t>0.0002,0.9972,0.0076,0.0058</t>
-  </si>
-  <si>
-    <t>0.0003,0.9746,0.5780,0.0010</t>
-  </si>
-  <si>
-    <t>0.0014,0.9979,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.0492,0.9265,0.0990,0.0015</t>
-  </si>
-  <si>
-    <t>0.5435,0.3966,0.0528,0.0026</t>
-  </si>
-  <si>
-    <t>0.9946,0.0024,0.0011,0.0006</t>
-  </si>
-  <si>
-    <t>0.9970,0.0009,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9945,0.0011,0.0019,0.0008</t>
-  </si>
-  <si>
-    <t>0.9933,0.0009,0.0015,0.0024</t>
-  </si>
-  <si>
-    <t>0.9987,0.0001,0.0000,0.0006</t>
-  </si>
-  <si>
-    <t>0.9954,0.0015,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.9863,0.0038,0.0008,0.0057</t>
-  </si>
-  <si>
-    <t>0.9951,0.0012,0.0011,0.0007</t>
-  </si>
-  <si>
-    <t>0.0008,0.9267,0.9436,0.0004</t>
-  </si>
-  <si>
-    <t>0.0017,0.9619,0.6380,0.0005</t>
-  </si>
-  <si>
-    <t>0.0057,0.3129,0.9788,0.0022</t>
-  </si>
-  <si>
-    <t>0.0192,0.0409,0.9393,0.0021</t>
-  </si>
-  <si>
-    <t>0.9961,0.0004,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.7738,0.0173,0.1914,0.0134</t>
-  </si>
-  <si>
-    <t>0.0556,0.0011,0.9647,0.0016</t>
-  </si>
-  <si>
-    <t>0.8610,0.0167,0.1489,0.0097</t>
-  </si>
-  <si>
-    <t>0.2433,0.0045,0.0008,0.8992</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.0027,0.9995</t>
-  </si>
-  <si>
-    <t>0.0005,0.0012,0.0032,0.9975</t>
-  </si>
-  <si>
-    <t>0.0014,0.0003,0.0005,0.9990</t>
-  </si>
-  <si>
-    <t>0.0005,0.9530,0.3802,0.0006</t>
-  </si>
-  <si>
-    <t>0.9943,0.0022,0.0007,0.0009</t>
-  </si>
-  <si>
-    <t>0.0218,0.9626,0.0148,0.0213</t>
-  </si>
-  <si>
-    <t>0.9961,0.0009,0.0007,0.0007</t>
-  </si>
-  <si>
-    <t>0.6581,0.3714,0.0387,0.0110</t>
-  </si>
-  <si>
-    <t>0.9838,0.0026,0.0021,0.0080</t>
-  </si>
-  <si>
-    <t>0.0524,0.0079,0.0031,0.9759</t>
-  </si>
-  <si>
-    <t>0.9912,0.0017,0.0009,0.0041</t>
-  </si>
-  <si>
-    <t>0.0004,0.0023,0.9965,0.0093</t>
-  </si>
-  <si>
-    <t>0.5938,0.0022,0.0071,0.6000</t>
-  </si>
-  <si>
-    <t>0.5867,0.0209,0.0040,0.6672</t>
-  </si>
-  <si>
-    <t>0.7607,0.2136,0.0300,0.0040</t>
-  </si>
-  <si>
-    <t>0.9794,0.0129,0.0037,0.0015</t>
-  </si>
-  <si>
-    <t>0.9868,0.0050,0.0037,0.0010</t>
-  </si>
-  <si>
-    <t>0.2054,0.6747,0.0578,0.0026</t>
-  </si>
-  <si>
-    <t>0.9590,0.0245,0.0108,0.0019</t>
-  </si>
-  <si>
-    <t>0.9398,0.0476,0.0087,0.0008</t>
-  </si>
-  <si>
-    <t>0.9624,0.0264,0.0096,0.0046</t>
-  </si>
-  <si>
-    <t>0.9891,0.0045,0.0023,0.0037</t>
-  </si>
-  <si>
-    <t>0.9932,0.0019,0.0023,0.0010</t>
-  </si>
-  <si>
-    <t>0.9949,0.0005,0.0011,0.0026</t>
-  </si>
-  <si>
-    <t>0.9925,0.0016,0.0029,0.0014</t>
-  </si>
-  <si>
-    <t>0.9947,0.0033,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9893,0.0051,0.0009,0.0031</t>
-  </si>
-  <si>
-    <t>0.9926,0.0016,0.0018,0.0024</t>
-  </si>
-  <si>
-    <t>0.6431,0.3447,0.0255,0.0079</t>
-  </si>
-  <si>
-    <t>0.6281,0.5117,0.0040,0.0012</t>
-  </si>
-  <si>
-    <t>0.7493,0.3613,0.0053,0.0008</t>
-  </si>
-  <si>
-    <t>0.7412,0.1856,0.0694,0.0126</t>
-  </si>
-  <si>
-    <t>0.9857,0.0127,0.0005,0.0018</t>
-  </si>
-  <si>
-    <t>0.9593,0.0205,0.0148,0.0043</t>
-  </si>
-  <si>
-    <t>0.9878,0.0058,0.0026,0.0009</t>
-  </si>
-  <si>
-    <t>0.9290,0.0756,0.0032,0.0085</t>
-  </si>
-  <si>
-    <t>0.0019,0.0176,0.9980,0.0007</t>
-  </si>
-  <si>
-    <t>0.8115,0.1169,0.0435,0.0009</t>
-  </si>
-  <si>
-    <t>0.0001,0.0014,0.9990,0.0006</t>
-  </si>
-  <si>
-    <t>0.0008,0.0169,0.9972,0.0006</t>
-  </si>
-  <si>
-    <t>0.0125,0.0008,0.9916,0.0004</t>
-  </si>
-  <si>
-    <t>0.0176,0.1993,0.9366,0.0024</t>
-  </si>
-  <si>
-    <t>0.0009,0.0027,0.9984,0.0002</t>
-  </si>
-  <si>
-    <t>0.0030,0.0010,0.9973,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.0038,0.9978,0.0005</t>
-  </si>
-  <si>
-    <t>0.0588,0.0036,0.9539,0.0030</t>
-  </si>
-  <si>
-    <t>0.1164,0.0053,0.9181,0.0024</t>
-  </si>
-  <si>
-    <t>0.2192,0.0016,0.8822,0.0017</t>
-  </si>
-  <si>
-    <t>0.0473,0.3600,0.6196,0.0020</t>
-  </si>
-  <si>
-    <t>0.0108,0.4174,0.7099,0.0002</t>
-  </si>
-  <si>
-    <t>0.7319,0.0175,0.3266,0.0025</t>
-  </si>
-  <si>
-    <t>0.1584,0.0119,0.8279,0.0284</t>
-  </si>
-  <si>
-    <t>0.1330,0.0088,0.8729,0.0085</t>
-  </si>
-  <si>
-    <t>0.1100,0.9352,0.0012,0.0008</t>
-  </si>
-  <si>
-    <t>0.0381,0.9598,0.0079,0.0022</t>
-  </si>
-  <si>
-    <t>0.9457,0.1083,0.0010,0.0007</t>
-  </si>
-  <si>
-    <t>0.9821,0.0139,0.0036,0.0012</t>
-  </si>
-  <si>
-    <t>0.8351,0.2722,0.0062,0.0024</t>
-  </si>
-  <si>
-    <t>0.6098,0.0972,0.2630,0.0127</t>
-  </si>
-  <si>
-    <t>0.9718,0.0018,0.0247,0.0011</t>
-  </si>
-  <si>
-    <t>0.8059,0.0101,0.1558,0.0333</t>
-  </si>
-  <si>
-    <t>0.8334,0.0082,0.2332,0.0027</t>
-  </si>
-  <si>
-    <t>0.6519,0.0015,0.4394,0.0035</t>
-  </si>
-  <si>
-    <t>0.0333,0.0064,0.9643,0.0099</t>
-  </si>
-  <si>
-    <t>0.0022,0.0494,0.9827,0.0042</t>
-  </si>
-  <si>
-    <t>0.0020,0.0265,0.9904,0.0029</t>
-  </si>
-  <si>
-    <t>0.0097,0.0059,0.9715,0.0061</t>
-  </si>
-  <si>
-    <t>0.0041,0.0173,0.9690,0.0050</t>
-  </si>
-  <si>
-    <t>0.9867,0.0090,0.0006,0.0019</t>
-  </si>
-  <si>
-    <t>0.9666,0.0242,0.0066,0.0009</t>
-  </si>
-  <si>
-    <t>0.9653,0.0158,0.0018,0.0096</t>
-  </si>
-  <si>
-    <t>0.9759,0.0250,0.0023,0.0008</t>
-  </si>
-  <si>
-    <t>0.9529,0.0554,0.0020,0.0030</t>
-  </si>
-  <si>
-    <t>0.9783,0.0202,0.0025,0.0007</t>
-  </si>
-  <si>
-    <t>0.9578,0.0229,0.0190,0.0024</t>
-  </si>
-  <si>
-    <t>0.9892,0.0038,0.0016,0.0039</t>
-  </si>
-  <si>
-    <t>0.0078,0.0128,0.9921,0.0005</t>
-  </si>
-  <si>
-    <t>0.0137,0.0270,0.9319,0.0115</t>
-  </si>
-  <si>
-    <t>0.7759,0.0117,0.2608,0.0068</t>
-  </si>
-  <si>
-    <t>0.0080,0.0023,0.9938,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0014,0.9980,0.0004</t>
-  </si>
-  <si>
-    <t>0.0047,0.0688,0.9831,0.0009</t>
-  </si>
-  <si>
-    <t>0.0011,0.0023,0.9979,0.0001</t>
-  </si>
-  <si>
-    <t>0.0381,0.0036,0.9573,0.0042</t>
-  </si>
-  <si>
-    <t>0.0053,0.0017,0.9907,0.0013</t>
-  </si>
-  <si>
-    <t>0.0036,0.0024,0.9930,0.0004</t>
-  </si>
-  <si>
-    <t>0.0065,0.0656,0.9593,0.0101</t>
-  </si>
-  <si>
-    <t>0.9289,0.0034,0.0590,0.0070</t>
-  </si>
-  <si>
-    <t>0.1909,0.0029,0.9024,0.0020</t>
-  </si>
-  <si>
-    <t>0.9428,0.0051,0.0232,0.0174</t>
-  </si>
-  <si>
-    <t>0.9626,0.0319,0.0081,0.0050</t>
-  </si>
-  <si>
-    <t>0.9936,0.0063,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9952,0.0030,0.0004,0.0008</t>
-  </si>
-  <si>
-    <t>0.9654,0.0508,0.0015,0.0012</t>
-  </si>
-  <si>
-    <t>0.9956,0.0012,0.0009,0.0012</t>
-  </si>
-  <si>
-    <t>0.9864,0.0121,0.0018,0.0012</t>
-  </si>
-  <si>
-    <t>0.9716,0.0233,0.0037,0.0004</t>
-  </si>
-  <si>
-    <t>0.9919,0.0037,0.0007,0.0022</t>
-  </si>
-  <si>
-    <t>0.0005,0.0087,0.9976,0.0001</t>
-  </si>
-  <si>
-    <t>0.0023,0.3626,0.9876,0.0010</t>
-  </si>
-  <si>
-    <t>0.0655,0.0170,0.9381,0.0017</t>
-  </si>
-  <si>
-    <t>0.0043,0.2483,0.8885,0.0029</t>
-  </si>
-  <si>
-    <t>0.0141,0.0016,0.9843,0.0015</t>
-  </si>
-  <si>
-    <t>0.0029,0.0038,0.9606,0.1892</t>
-  </si>
-  <si>
-    <t>0.0842,0.0046,0.8693,0.0705</t>
-  </si>
-  <si>
-    <t>0.0396,0.0082,0.9436,0.0085</t>
-  </si>
-  <si>
-    <t>0.6587,0.0010,0.0020,0.6346</t>
-  </si>
-  <si>
-    <t>0.0315,0.0261,0.0010,0.9865</t>
-  </si>
-  <si>
-    <t>0.4097,0.0012,0.0004,0.8660</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0014,0.9992</t>
-  </si>
-  <si>
-    <t>0.0038,0.0003,0.0001,0.9982</t>
-  </si>
-  <si>
-    <t>0.7555,0.0096,0.0041,0.4325</t>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,1,1</t>
+  </si>
+  <si>
+    <t>0.7639,0.0903,0.0828,0.0768</t>
+  </si>
+  <si>
+    <t>0.0032,0.0024,0.0000,0.9986</t>
+  </si>
+  <si>
+    <t>0.8244,0.0143,0.0013,0.1938</t>
+  </si>
+  <si>
+    <t>0.0108,0.0153,0.0013,0.9931</t>
+  </si>
+  <si>
+    <t>0.9962,0.0010,0.0007,0.0008</t>
+  </si>
+  <si>
+    <t>0.9962,0.0006,0.0010,0.0010</t>
+  </si>
+  <si>
+    <t>0.9870,0.0062,0.0026,0.0013</t>
+  </si>
+  <si>
+    <t>0.9930,0.0022,0.0025,0.0014</t>
+  </si>
+  <si>
+    <t>0.9903,0.0069,0.0011,0.0009</t>
+  </si>
+  <si>
+    <t>0.9920,0.0059,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9981,0.0004,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9926,0.0016,0.0012,0.0030</t>
+  </si>
+  <si>
+    <t>0.9297,0.0165,0.0250,0.0001</t>
+  </si>
+  <si>
+    <t>0.0372,0.0270,0.9528,0.0036</t>
+  </si>
+  <si>
+    <t>0.2078,0.0026,0.9250,0.0001</t>
+  </si>
+  <si>
+    <t>0.1685,0.0137,0.8490,0.0004</t>
+  </si>
+  <si>
+    <t>0.9579,0.0083,0.0278,0.0011</t>
+  </si>
+  <si>
+    <t>0.0005,0.9985,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0024,0.9932,0.0024,0.0007</t>
+  </si>
+  <si>
+    <t>0.0623,0.9207,0.0194,0.0085</t>
+  </si>
+  <si>
+    <t>0.0181,0.9752,0.0078,0.0025</t>
+  </si>
+  <si>
+    <t>0.0011,0.9969,0.0021,0.0007</t>
+  </si>
+  <si>
+    <t>0.2763,0.0037,0.7542,0.0130</t>
+  </si>
+  <si>
+    <t>0.4519,0.0019,0.6879,0.0009</t>
+  </si>
+  <si>
+    <t>0.0004,0.0012,0.9986,0.0005</t>
+  </si>
+  <si>
+    <t>0.0178,0.0064,0.9770,0.0015</t>
+  </si>
+  <si>
+    <t>0.0326,0.0071,0.9487,0.0196</t>
+  </si>
+  <si>
+    <t>0.0034,0.0020,0.9945,0.0004</t>
+  </si>
+  <si>
+    <t>0.0010,0.0003,0.9970,0.0008</t>
+  </si>
+  <si>
+    <t>0.9580,0.0412,0.0037,0.0003</t>
+  </si>
+  <si>
+    <t>0.4511,0.4078,0.0921,0.0045</t>
+  </si>
+  <si>
+    <t>0.0036,0.0726,0.9894,0.0055</t>
+  </si>
+  <si>
+    <t>0.0266,0.9065,0.0729,0.0003</t>
+  </si>
+  <si>
+    <t>0.9821,0.0068,0.0030,0.0024</t>
+  </si>
+  <si>
+    <t>0.8881,0.0393,0.0819,0.0064</t>
+  </si>
+  <si>
+    <t>0.8163,0.0673,0.1174,0.0092</t>
+  </si>
+  <si>
+    <t>0.0023,0.9932,0.1382,0.0008</t>
+  </si>
+  <si>
+    <t>0.0066,0.2545,0.9204,0.0083</t>
+  </si>
+  <si>
+    <t>0.0189,0.0094,0.9772,0.0010</t>
+  </si>
+  <si>
+    <t>0.1180,0.0116,0.9070,0.0027</t>
+  </si>
+  <si>
+    <t>0.0127,0.0046,0.9470,0.0388</t>
+  </si>
+  <si>
+    <t>0.0023,0.6646,0.9718,0.0031</t>
+  </si>
+  <si>
+    <t>0.0003,0.9982,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.0032,0.0028,0.9946,0.0004</t>
+  </si>
+  <si>
+    <t>0.0213,0.8661,0.1628,0.5567</t>
+  </si>
+  <si>
+    <t>0.0017,0.9897,0.0070,0.0066</t>
+  </si>
+  <si>
+    <t>0.0006,0.9947,0.0083,0.0049</t>
+  </si>
+  <si>
+    <t>0.0006,0.9961,0.0065,0.0021</t>
+  </si>
+  <si>
+    <t>0.0027,0.0115,0.9910,0.0017</t>
+  </si>
+  <si>
+    <t>0.0103,0.3661,0.9787,0.0012</t>
+  </si>
+  <si>
+    <t>0.0038,0.0032,0.9861,0.0029</t>
+  </si>
+  <si>
+    <t>0.0011,0.0009,0.9975,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.0019,0.9981,0.0013</t>
+  </si>
+  <si>
+    <t>0.0112,0.0140,0.9878,0.0003</t>
+  </si>
+  <si>
+    <t>0.2802,0.8079,0.0037,0.0021</t>
+  </si>
+  <si>
+    <t>0.9518,0.0190,0.0229,0.0071</t>
+  </si>
+  <si>
+    <t>0.3310,0.7330,0.0135,0.0085</t>
+  </si>
+  <si>
+    <t>0.0023,0.0044,0.9957,0.0037</t>
+  </si>
+  <si>
+    <t>0.9885,0.0039,0.0034,0.0026</t>
+  </si>
+  <si>
+    <t>0.9872,0.0105,0.0012,0.0011</t>
+  </si>
+  <si>
+    <t>0.9897,0.0085,0.0010,0.0006</t>
+  </si>
+  <si>
+    <t>0.0004,0.9884,0.9166,0.0002</t>
+  </si>
+  <si>
+    <t>0.0076,0.0201,0.9816,0.0030</t>
+  </si>
+  <si>
+    <t>0.0008,0.0023,0.9956,0.0017</t>
+  </si>
+  <si>
+    <t>0.0003,0.9811,0.9831,0.0004</t>
+  </si>
+  <si>
+    <t>0.0004,0.0270,0.9972,0.0029</t>
+  </si>
+  <si>
+    <t>0.0117,0.9855,0.0039,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.9975,0.0045,0.0001</t>
+  </si>
+  <si>
+    <t>0.6705,0.0153,0.4648,0.0068</t>
+  </si>
+  <si>
+    <t>0.7183,0.0500,0.2155,0.0019</t>
+  </si>
+  <si>
+    <t>0.0005,0.0235,0.9985,0.0003</t>
+  </si>
+  <si>
+    <t>0.0042,0.8936,0.9377,0.0030</t>
+  </si>
+  <si>
+    <t>0.0037,0.4745,0.9744,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.9984,0.5664,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.9883,0.9555,0.0002</t>
+  </si>
+  <si>
+    <t>0.0100,0.0013,0.0654,0.9702</t>
+  </si>
+  <si>
+    <t>0.0007,0.0021,0.0002,0.9992</t>
+  </si>
+  <si>
+    <t>0.0005,0.0235,0.0017,0.9977</t>
+  </si>
+  <si>
+    <t>0.0024,0.0068,0.0024,0.9961</t>
+  </si>
+  <si>
+    <t>0.0020,0.0012,0.0011,0.9979</t>
+  </si>
+  <si>
+    <t>0.0018,0.0004,0.0067,0.9962</t>
+  </si>
+  <si>
+    <t>0.0004,0.9864,0.8796,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.9574,0.9923,0.0001</t>
+  </si>
+  <si>
+    <t>0.0229,0.2466,0.8274,0.0005</t>
+  </si>
+  <si>
+    <t>0.0006,0.8520,0.9872,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.9816,0.9772,0.0000</t>
+  </si>
+  <si>
+    <t>0.0282,0.4835,0.7717,0.0010</t>
+  </si>
+  <si>
+    <t>0.9961,0.0023,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9972,0.0017,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9920,0.0063,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9952,0.0015,0.0004,0.0016</t>
+  </si>
+  <si>
+    <t>0.8973,0.1446,0.0066,0.0039</t>
+  </si>
+  <si>
+    <t>0.9947,0.0028,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9917,0.0038,0.0015,0.0016</t>
+  </si>
+  <si>
+    <t>0.9942,0.0029,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.9919,0.0028,0.0021,0.0022</t>
+  </si>
+  <si>
+    <t>0.9937,0.0018,0.0024,0.0006</t>
+  </si>
+  <si>
+    <t>0.9940,0.0022,0.0006,0.0013</t>
+  </si>
+  <si>
+    <t>0.9964,0.0006,0.0014,0.0006</t>
+  </si>
+  <si>
+    <t>0.9944,0.0015,0.0004,0.0018</t>
+  </si>
+  <si>
+    <t>0.9958,0.0015,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.9974,0.0005,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9942,0.0010,0.0007,0.0028</t>
+  </si>
+  <si>
+    <t>0.0003,0.0004,0.9975,0.0065</t>
+  </si>
+  <si>
+    <t>0.0185,0.0016,0.9405,0.0643</t>
+  </si>
+  <si>
+    <t>0.9695,0.0020,0.0175,0.0020</t>
+  </si>
+  <si>
+    <t>0.0010,0.0007,0.9980,0.0005</t>
+  </si>
+  <si>
+    <t>0.0083,0.9859,0.0006,0.0020</t>
+  </si>
+  <si>
+    <t>0.0012,0.9961,0.0012,0.0007</t>
+  </si>
+  <si>
+    <t>0.0055,0.9895,0.0012,0.0014</t>
+  </si>
+  <si>
+    <t>0.0183,0.9760,0.0044,0.0014</t>
+  </si>
+  <si>
+    <t>0.0037,0.9935,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.0031,0.9930,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.7915,0.2513,0.0083,0.0015</t>
+  </si>
+  <si>
+    <t>0.6233,0.0356,0.4153,0.0097</t>
+  </si>
+  <si>
+    <t>0.2563,0.0048,0.8525,0.0013</t>
+  </si>
+  <si>
+    <t>0.6364,0.1222,0.0700,0.0610</t>
+  </si>
+  <si>
+    <t>0.6789,0.0158,0.3777,0.0024</t>
+  </si>
+  <si>
+    <t>0.0559,0.4999,0.3816,0.4079</t>
+  </si>
+  <si>
+    <t>0.0004,0.9966,0.0086,0.0003</t>
+  </si>
+  <si>
+    <t>0.0018,0.9883,0.0092,0.0053</t>
+  </si>
+  <si>
+    <t>0.0003,0.9959,0.0074,0.0261</t>
+  </si>
+  <si>
+    <t>0.0004,0.9807,0.5599,0.0002</t>
+  </si>
+  <si>
+    <t>0.0009,0.9978,0.0040,0.0003</t>
+  </si>
+  <si>
+    <t>0.5335,0.4481,0.0501,0.0018</t>
+  </si>
+  <si>
+    <t>0.6727,0.3191,0.0348,0.0072</t>
+  </si>
+  <si>
+    <t>0.9955,0.0014,0.0008,0.0011</t>
+  </si>
+  <si>
+    <t>0.9906,0.0031,0.0014,0.0027</t>
+  </si>
+  <si>
+    <t>0.9915,0.0020,0.0012,0.0026</t>
+  </si>
+  <si>
+    <t>0.9636,0.0111,0.0127,0.0122</t>
+  </si>
+  <si>
+    <t>0.9936,0.0025,0.0010,0.0010</t>
+  </si>
+  <si>
+    <t>0.9972,0.0004,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9847,0.0062,0.0022,0.0034</t>
+  </si>
+  <si>
+    <t>0.9899,0.0020,0.0041,0.0019</t>
+  </si>
+  <si>
+    <t>0.0008,0.8428,0.9644,0.0008</t>
+  </si>
+  <si>
+    <t>0.0020,0.9494,0.4229,0.0005</t>
+  </si>
+  <si>
+    <t>0.0020,0.0045,0.9939,0.0014</t>
+  </si>
+  <si>
+    <t>0.0565,0.0075,0.9226,0.0004</t>
+  </si>
+  <si>
+    <t>0.9958,0.0008,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.4843,0.0098,0.6497,0.0025</t>
+  </si>
+  <si>
+    <t>0.1028,0.0007,0.9550,0.0006</t>
+  </si>
+  <si>
+    <t>0.8212,0.0344,0.1541,0.0122</t>
+  </si>
+  <si>
+    <t>0.0560,0.0031,0.0080,0.9610</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0033,0.9995</t>
+  </si>
+  <si>
+    <t>0.0027,0.0053,0.0077,0.9927</t>
+  </si>
+  <si>
+    <t>0.0013,0.0003,0.0003,0.9991</t>
+  </si>
+  <si>
+    <t>0.0008,0.9111,0.4221,0.0012</t>
+  </si>
+  <si>
+    <t>0.9922,0.0022,0.0008,0.0022</t>
+  </si>
+  <si>
+    <t>0.0100,0.9808,0.0047,0.0350</t>
+  </si>
+  <si>
+    <t>0.9959,0.0014,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.8006,0.2057,0.0484,0.0160</t>
+  </si>
+  <si>
+    <t>0.9815,0.0058,0.0028,0.0057</t>
+  </si>
+  <si>
+    <t>0.0726,0.0006,0.0032,0.9741</t>
+  </si>
+  <si>
+    <t>0.9700,0.0035,0.0037,0.0280</t>
+  </si>
+  <si>
+    <t>0.0002,0.0050,0.9962,0.0206</t>
+  </si>
+  <si>
+    <t>0.7400,0.0057,0.0041,0.5477</t>
+  </si>
+  <si>
+    <t>0.7293,0.0124,0.0134,0.4603</t>
+  </si>
+  <si>
+    <t>0.6001,0.4335,0.0077,0.0066</t>
+  </si>
+  <si>
+    <t>0.9556,0.0243,0.0068,0.0097</t>
+  </si>
+  <si>
+    <t>0.9644,0.0122,0.0122,0.0033</t>
+  </si>
+  <si>
+    <t>0.5345,0.5553,0.0037,0.0039</t>
+  </si>
+  <si>
+    <t>0.9732,0.0266,0.0026,0.0008</t>
+  </si>
+  <si>
+    <t>0.9836,0.0092,0.0027,0.0009</t>
+  </si>
+  <si>
+    <t>0.9729,0.0066,0.0147,0.0129</t>
+  </si>
+  <si>
+    <t>0.9903,0.0023,0.0014,0.0056</t>
+  </si>
+  <si>
+    <t>0.9971,0.0008,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9955,0.0012,0.0013,0.0010</t>
+  </si>
+  <si>
+    <t>0.9911,0.0025,0.0039,0.0011</t>
+  </si>
+  <si>
+    <t>0.9854,0.0059,0.0031,0.0023</t>
+  </si>
+  <si>
+    <t>0.9852,0.0033,0.0061,0.0045</t>
+  </si>
+  <si>
+    <t>0.9911,0.0015,0.0018,0.0037</t>
+  </si>
+  <si>
+    <t>0.6298,0.3886,0.0111,0.0037</t>
+  </si>
+  <si>
+    <t>0.5903,0.5114,0.0041,0.0038</t>
+  </si>
+  <si>
+    <t>0.8775,0.1652,0.0047,0.0010</t>
+  </si>
+  <si>
+    <t>0.6821,0.2270,0.0880,0.0062</t>
+  </si>
+  <si>
+    <t>0.9651,0.0407,0.0020,0.0013</t>
+  </si>
+  <si>
+    <t>0.9689,0.0133,0.0069,0.0085</t>
+  </si>
+  <si>
+    <t>0.9828,0.0087,0.0052,0.0009</t>
+  </si>
+  <si>
+    <t>0.9625,0.0291,0.0007,0.0036</t>
+  </si>
+  <si>
+    <t>0.0005,0.0565,0.9988,0.0010</t>
+  </si>
+  <si>
+    <t>0.7447,0.1022,0.1711,0.0053</t>
+  </si>
+  <si>
+    <t>0.0002,0.0008,0.9992,0.0003</t>
+  </si>
+  <si>
+    <t>0.0006,0.0191,0.9973,0.0003</t>
+  </si>
+  <si>
+    <t>0.0063,0.0035,0.9923,0.0023</t>
+  </si>
+  <si>
+    <t>0.0119,0.5019,0.9142,0.0013</t>
+  </si>
+  <si>
+    <t>0.0006,0.0061,0.9981,0.0003</t>
+  </si>
+  <si>
+    <t>0.0027,0.0020,0.9957,0.0003</t>
+  </si>
+  <si>
+    <t>0.0027,0.0020,0.9969,0.0002</t>
+  </si>
+  <si>
+    <t>0.0273,0.1911,0.4502,0.1213</t>
+  </si>
+  <si>
+    <t>0.0502,0.0030,0.9651,0.0027</t>
+  </si>
+  <si>
+    <t>0.2240,0.0079,0.8446,0.0054</t>
+  </si>
+  <si>
+    <t>0.4147,0.3518,0.0767,0.0010</t>
+  </si>
+  <si>
+    <t>0.2556,0.2173,0.2791,0.0007</t>
+  </si>
+  <si>
+    <t>0.9146,0.0476,0.0289,0.0073</t>
+  </si>
+  <si>
+    <t>0.4323,0.0072,0.6861,0.0055</t>
+  </si>
+  <si>
+    <t>0.0192,0.0542,0.9011,0.0017</t>
+  </si>
+  <si>
+    <t>0.4164,0.7136,0.0038,0.0010</t>
+  </si>
+  <si>
+    <t>0.4712,0.6995,0.0015,0.0010</t>
+  </si>
+  <si>
+    <t>0.7986,0.3845,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.9581,0.0430,0.0054,0.0061</t>
+  </si>
+  <si>
+    <t>0.5000,0.6356,0.0034,0.0021</t>
+  </si>
+  <si>
+    <t>0.6291,0.0704,0.2846,0.0267</t>
+  </si>
+  <si>
+    <t>0.9930,0.0005,0.0028,0.0007</t>
+  </si>
+  <si>
+    <t>0.8958,0.0059,0.0179,0.0513</t>
+  </si>
+  <si>
+    <t>0.7112,0.0303,0.2960,0.0180</t>
+  </si>
+  <si>
+    <t>0.9180,0.0031,0.1076,0.0012</t>
+  </si>
+  <si>
+    <t>0.0079,0.0059,0.9734,0.0333</t>
+  </si>
+  <si>
+    <t>0.0084,0.0681,0.8436,0.0585</t>
+  </si>
+  <si>
+    <t>0.0114,0.0219,0.9779,0.0014</t>
+  </si>
+  <si>
+    <t>0.0844,0.0225,0.9173,0.0014</t>
+  </si>
+  <si>
+    <t>0.0067,0.9279,0.1622,0.0010</t>
+  </si>
+  <si>
+    <t>0.9878,0.0068,0.0027,0.0014</t>
+  </si>
+  <si>
+    <t>0.9903,0.0043,0.0027,0.0007</t>
+  </si>
+  <si>
+    <t>0.9697,0.0309,0.0009,0.0014</t>
+  </si>
+  <si>
+    <t>0.9639,0.0448,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.9722,0.0187,0.0096,0.0034</t>
+  </si>
+  <si>
+    <t>0.9820,0.0123,0.0032,0.0021</t>
+  </si>
+  <si>
+    <t>0.9818,0.0065,0.0071,0.0031</t>
+  </si>
+  <si>
+    <t>0.9965,0.0004,0.0004,0.0014</t>
+  </si>
+  <si>
+    <t>0.0029,0.0211,0.9942,0.0038</t>
+  </si>
+  <si>
+    <t>0.0114,0.0909,0.9446,0.0043</t>
+  </si>
+  <si>
+    <t>0.8038,0.0040,0.1629,0.0087</t>
+  </si>
+  <si>
+    <t>0.0020,0.0018,0.9968,0.0003</t>
+  </si>
+  <si>
+    <t>0.0010,0.0021,0.9981,0.0001</t>
+  </si>
+  <si>
+    <t>0.0118,0.0266,0.9762,0.0018</t>
+  </si>
+  <si>
+    <t>0.0008,0.0082,0.9972,0.0004</t>
+  </si>
+  <si>
+    <t>0.0049,0.0025,0.9893,0.0032</t>
+  </si>
+  <si>
+    <t>0.0029,0.0149,0.9965,0.0002</t>
+  </si>
+  <si>
+    <t>0.0049,0.0113,0.9883,0.0014</t>
+  </si>
+  <si>
+    <t>0.0704,0.0407,0.8623,0.0154</t>
+  </si>
+  <si>
+    <t>0.8195,0.0062,0.2355,0.0018</t>
+  </si>
+  <si>
+    <t>0.7873,0.0013,0.4419,0.0004</t>
+  </si>
+  <si>
+    <t>0.9737,0.0038,0.0153,0.0014</t>
+  </si>
+  <si>
+    <t>0.9445,0.0517,0.0110,0.0056</t>
+  </si>
+  <si>
+    <t>0.9969,0.0025,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9879,0.0051,0.0040,0.0019</t>
+  </si>
+  <si>
+    <t>0.9892,0.0049,0.0037,0.0012</t>
+  </si>
+  <si>
+    <t>0.9937,0.0018,0.0006,0.0034</t>
+  </si>
+  <si>
+    <t>0.9904,0.0055,0.0022,0.0011</t>
+  </si>
+  <si>
+    <t>0.9843,0.0133,0.0020,0.0007</t>
+  </si>
+  <si>
+    <t>0.9908,0.0043,0.0017,0.0017</t>
+  </si>
+  <si>
+    <t>0.0354,0.0787,0.9004,0.0016</t>
+  </si>
+  <si>
+    <t>0.0003,0.8566,0.9936,0.0002</t>
+  </si>
+  <si>
+    <t>0.0118,0.0071,0.9787,0.0023</t>
+  </si>
+  <si>
+    <t>0.0231,0.0072,0.9664,0.0032</t>
+  </si>
+  <si>
+    <t>0.1089,0.0026,0.9234,0.0008</t>
+  </si>
+  <si>
+    <t>0.0275,0.0025,0.6538,0.5964</t>
+  </si>
+  <si>
+    <t>0.1282,0.0189,0.8092,0.0791</t>
+  </si>
+  <si>
+    <t>0.0609,0.0122,0.8861,0.0253</t>
+  </si>
+  <si>
+    <t>0.9304,0.0007,0.0016,0.1204</t>
+  </si>
+  <si>
+    <t>0.0291,0.0199,0.0009,0.9883</t>
+  </si>
+  <si>
+    <t>0.0414,0.0008,0.0013,0.9843</t>
+  </si>
+  <si>
+    <t>0.0012,0.0001,0.0016,0.9986</t>
+  </si>
+  <si>
+    <t>0.0039,0.0010,0.0001,0.9976</t>
+  </si>
+  <si>
+    <t>0.6004,0.0170,0.0025,0.6162</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1971,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1985,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1999,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2013,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2027,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2041,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2055,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2069,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2083,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2097,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2111,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2125,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2139,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,10 +2150,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2167,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2181,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2195,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2209,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2223,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2237,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2251,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2265,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,7 +2279,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2293,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2307,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2321,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2335,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2349,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2363,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2377,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2388,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2405,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,10 +2416,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2433,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,10 +2444,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2458,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2475,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2486,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2503,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2517,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2531,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,10 +2542,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2559,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2573,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2584,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2601,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2615,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2629,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2643,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,10 +2654,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2671,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2685,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2699,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2713,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,10 +2724,10 @@
         <v>259</v>
       </c>
       <c r="C56" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2741,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,10 +2752,10 @@
         <v>259</v>
       </c>
       <c r="C58" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2769,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2783,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2797,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2811,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2825,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2839,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2853,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2867,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2881,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2895,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2909,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2923,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,10 +2934,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2951,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2965,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,10 +2976,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,10 +2990,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3007,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3021,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3035,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3049,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3063,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3077,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3091,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3105,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3119,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,10 +3130,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3147,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3161,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,10 +3172,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3189,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3203,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3217,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3231,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3245,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3259,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3273,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3287,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3301,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3315,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3329,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3343,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3357,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3371,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3385,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3399,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3413,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3427,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3441,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3455,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3469,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3483,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3497,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3511,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3525,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3539,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3550,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3567,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3581,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,7 +3595,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,7 +3609,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,10 +3620,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3637,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3651,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3665,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3679,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3693,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,10 +3704,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3721,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3735,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3749,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3763,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3777,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3791,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3805,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3819,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3833,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3847,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,10 +3858,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3875,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3889,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3903,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,10 +3914,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3931,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3945,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3959,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3973,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3987,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +4001,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4015,7 @@
         <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4029,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4043,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4057,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4071,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4085,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4099,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4113,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4127,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,10 +4138,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,10 +4152,10 @@
         <v>259</v>
       </c>
       <c r="C158" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4169,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4183,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4197,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4208,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4225,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4239,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4253,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4267,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4281,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4295,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4309,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4323,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4337,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4351,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4365,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4376,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4393,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,7 +4407,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4421,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4435,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4449,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4463,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4477,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4491,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4505,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4519,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4533,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,10 +4544,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4561,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4575,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4589,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,10 +4600,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4617,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,7 +4631,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4642,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4656,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,7 +4673,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4687,7 @@
         <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4701,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4715,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4729,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4743,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4757,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,10 +4768,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4785,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4799,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4813,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,7 +4827,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4841,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4855,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4869,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4883,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4897,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,10 +4908,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4925,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4939,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4953,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4967,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4981,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4995,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5009,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5023,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5037,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5039,7 +5051,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5065,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5079,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5093,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5107,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5121,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5135,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5149,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5163,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5177,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5191,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,10 +5202,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5219,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5233,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5247,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5261,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5275,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5289,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5303,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5317,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5331,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5345,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,10 +5356,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5373,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5387,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5401,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5412,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5429,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5443,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,10 +5454,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5471,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5485,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5499,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5513,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,10 +5524,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
